--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0003T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0003T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>65.79228522081287</v>
+        <v>10.69124634838209</v>
       </c>
       <c r="D2" t="n">
-        <v>63.70456724087261</v>
+        <v>10.3519921766418</v>
       </c>
       <c r="E2" t="n">
-        <v>16.32254870179731</v>
+        <v>2.652414164042062</v>
       </c>
       <c r="F2" t="n">
-        <v>17.21115906658972</v>
+        <v>2.79681334832083</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>66.03384498471735</v>
+        <v>10.73049981001657</v>
       </c>
       <c r="D3" t="n">
-        <v>63.90177177100207</v>
+        <v>10.38403791278784</v>
       </c>
       <c r="E3" t="n">
-        <v>16.32254870179731</v>
+        <v>2.652414164042062</v>
       </c>
       <c r="F3" t="n">
-        <v>17.21115906658972</v>
+        <v>2.79681334832083</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>51.46748030809732</v>
+        <v>8.363465550065815</v>
       </c>
       <c r="D4" t="n">
-        <v>50.0182236825809</v>
+        <v>8.127961348419396</v>
       </c>
       <c r="E4" t="n">
-        <v>16.32254870179731</v>
+        <v>2.652414164042062</v>
       </c>
       <c r="F4" t="n">
-        <v>17.21115906658972</v>
+        <v>2.79681334832083</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>57.62403332637358</v>
+        <v>9.363905415535706</v>
       </c>
       <c r="D5" t="n">
-        <v>56.23821130673914</v>
+        <v>9.13870933734511</v>
       </c>
       <c r="E5" t="n">
-        <v>16.32254870179731</v>
+        <v>2.652414164042062</v>
       </c>
       <c r="F5" t="n">
-        <v>17.21115906658972</v>
+        <v>2.79681334832083</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.96219932694864</v>
+        <v>6.818857390629153</v>
       </c>
       <c r="D6" t="n">
-        <v>41.06684579047138</v>
+        <v>6.673362440951599</v>
       </c>
       <c r="E6" t="n">
-        <v>16.32254870179731</v>
+        <v>2.652414164042062</v>
       </c>
       <c r="F6" t="n">
-        <v>17.21115906658972</v>
+        <v>2.79681334832083</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>18.41136841953018</v>
+        <v>2.991847368173655</v>
       </c>
       <c r="D7" t="n">
-        <v>20.50701161830984</v>
+        <v>3.332389387975348</v>
       </c>
       <c r="E7" t="n">
-        <v>16.32254870179731</v>
+        <v>2.652414164042062</v>
       </c>
       <c r="F7" t="n">
-        <v>17.21115906658972</v>
+        <v>2.79681334832083</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.78340223269441</v>
+        <v>6.464802862812842</v>
       </c>
       <c r="D8" t="n">
-        <v>32.88462618219334</v>
+        <v>5.343751754606417</v>
       </c>
       <c r="E8" t="n">
-        <v>16.32254870179731</v>
+        <v>2.652414164042062</v>
       </c>
       <c r="F8" t="n">
-        <v>17.21115906658972</v>
+        <v>2.79681334832083</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.09960165829814</v>
+        <v>4.403685269473448</v>
       </c>
       <c r="D9" t="n">
-        <v>17.15424904874256</v>
+        <v>2.787565470420666</v>
       </c>
       <c r="E9" t="n">
-        <v>16.32254870179731</v>
+        <v>2.652414164042062</v>
       </c>
       <c r="F9" t="n">
-        <v>17.21115906658972</v>
+        <v>2.79681334832083</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
